--- a/static/templates/bulk_quota.xlsx
+++ b/static/templates/bulk_quota.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\nq57-catp\static\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C3480B-7821-4E49-85BE-CB3FA28A2FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8677FFFE-163A-4F39-A752-C827D7846E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Config" sheetId="2" r:id="rId2"/>
+    <sheet name="Import" sheetId="1" r:id="rId1"/>
+    <sheet name="Hướng dẫn" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="typeLookup">Table2[#All]</definedName>
+    <definedName name="typeLookup">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>Tên chỉ tiêu</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Tỉ lệ chuyển đổi số</t>
   </si>
   <si>
-    <t>Nhãn</t>
-  </si>
-  <si>
     <t>Số liệu trong kỳ báo cáo</t>
   </si>
   <si>
@@ -83,6 +80,42 @@
   </si>
   <si>
     <t>CAXAĐ_HCM,CAXAP_BD, CAXAN_HCM</t>
+  </si>
+  <si>
+    <t>Điền tên viết tắt của đơn vị. CHỈ ĐIỀN 1 ĐƠN VỊ THUỘC NHÓM ĐƠN VỊ CAP</t>
+  </si>
+  <si>
+    <t>Định dạng dd/mm/yyyy</t>
+  </si>
+  <si>
+    <t>Điền tên viết tắt của đơn vị. ĐIỀN NHIỀU ĐƠN VỊ CÁCH NHAU BỞI,</t>
+  </si>
+  <si>
+    <t>BẢNG ĐƠN VỊ</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Tên đơn vị</t>
+  </si>
+  <si>
+    <t>Tên viết tắt</t>
+  </si>
+  <si>
+    <t>Nhóm đơn vị</t>
+  </si>
+  <si>
+    <t>Điền từ 1 đến 100</t>
+  </si>
+  <si>
+    <t>Tham chiếu tới bảng đơn vị cột O</t>
+  </si>
+  <si>
+    <t>VUI LÒNG ĐIỀN VÀO Ở SHEET IMPORT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cách tính chọn 1 trong 2 cách </t>
   </si>
 </sst>
 </file>
@@ -92,18 +125,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -114,8 +139,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -124,18 +187,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -143,23 +200,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
@@ -169,21 +249,37 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -194,16 +290,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F79CD82-2C03-4849-90CF-D60855ADD9B9}" name="Table2" displayName="Table2" ref="A1:A3" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:A3" xr:uid="{8F79CD82-2C03-4849-90CF-D60855ADD9B9}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E2A68DAF-1FCA-4BD8-8E34-71B5D4562A7D}" name="Nhãn"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -472,85 +558,67 @@
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" style="6" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" style="7" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="19" style="3" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="4">
-        <v>90</v>
-      </c>
-      <c r="F2" s="5">
-        <v>46113</v>
-      </c>
-      <c r="G2" s="5">
-        <v>46173</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>16</v>
-      </c>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
     </row>
   </sheetData>
   <sheetProtection insertRows="0" selectLockedCells="1" selectUnlockedCells="1"/>
@@ -575,7 +643,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3381ADB9-3684-455B-8916-6D12173D36FE}">
           <x14:formula1>
-            <xm:f>Config!$A$2:$A$3</xm:f>
+            <xm:f>'Hướng dẫn'!#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>B1:B1048576</xm:sqref>
         </x14:dataValidation>
@@ -586,34 +654,153 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B61A8CE-C6B6-4305-A493-1D7FC44DCC79}">
-  <dimension ref="A1:A3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F9E7E6C-E690-4B46-9A53-0BC0AD0FCE28}">
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="12" max="12" width="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.5703125" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" spans="1:15" ht="104.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+    </row>
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>90.25</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46113</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46173</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
+    <row r="8" spans="1:15" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="C8" s="10" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="meZi9TQ3aOBfixJSjuk3+LnkbrW1+2qPQUwzALZYYgzRkUFln0rI5LecxDfIeEs+C+7WyfHDh7JMRb9TOTYbPQ==" saltValue="w0ZVZctc0LJtgVByFdTPnQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="L2:O2"/>
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="date" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F4" xr:uid="{7F82A98E-FA93-4795-94BA-7582E1A9281F}">
+      <formula1>G4</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G4" xr:uid="{5ACFCD0E-E01A-4F9C-8C7C-D1ABCF2A6ADB}">
+      <formula1>F3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4" xr:uid="{3246483E-0B21-43A0-A1CC-5C67E259DE68}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>